--- a/docs/jp/02_基本設計書.xlsx
+++ b/docs/jp/02_基本設計書.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>iTMS 株式会社 御中</t>
+          <t>統合G</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>(担当部門)</t>
+          <t>張　泊江</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>(担当部門)</t>
+          <t>張　泊江</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1154,191 +1154,156 @@
       </c>
     </row>
     <row r="4">
-      <c r="C4" s="18" t="inlineStr">
-        <is>
-          <t>出典: docs/jp/01_要件定義書.xlsx §1.5 + METHODOLOGY.md Purpose。</t>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>1.2 設計対象システムの範囲</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>1.2 設計対象システムの範囲</t>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>本書の設計対象は以下の 4 サブシステムである。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="C6" s="18" t="inlineStr">
         <is>
-          <t>本書の設計対象は以下の 4 サブシステムである。</t>
+          <t>(1) 知識ベース本体 — 臨床試験データ表形式モデル (SDTM: Study Data Tabulation Model) の CDISC 公式刊行物から抽出・再構成した 293 件の Markdown ファイル群。63 ドメイン・6 章・6 モデル文書・受控用語群・索引文書で構成される。現行運用中。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="C7" s="18" t="inlineStr">
         <is>
-          <t>(1) 知識ベース本体 — 臨床試験データ表形式モデル (SDTM: Study Data Tabulation Model) の CDISC 公式刊行物から抽出・再構成した 293 件の Markdown ファイル群。63 ドメイン・6 章・6 モデル文書・受控用語群・索引文書で構成される。現行運用中。</t>
+          <t>(2) 検証パイプライン — 知識ベース本体の各記述を出典 PDF と頁単位で照合する字面級確認の独立工程。検証単位データ schema (atom_schema v1.2 凍結済) および突合管理表データ schema (ledger_schema v1.2 凍結済) を基盤とする。現行運用中 (対象範囲の 97% 完了)。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="C8" s="18" t="inlineStr">
         <is>
-          <t>(2) 検証パイプライン — 知識ベース本体の各記述を出典 PDF と頁単位で照合する字面級確認の独立工程。検証単位データ schema (atom_schema v1.2 凍結済) および突合管理表データ schema (ledger_schema v1.2 凍結済) を基盤とする。現行運用中 (対象範囲の 97% 完了)。</t>
+          <t>(3) AI 平台展開 — 知識ベースを ChatGPT GPTs・Google Gemini Gems・Google NotebookLM・Anthropic Claude Projects の 4 平台向けに再パッケージしたリリース版 v1.0。現行運用中 (Phase 6.5 完了)。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="C9" s="18" t="inlineStr">
         <is>
-          <t>(3) AI 平台展開 — 知識ベースを ChatGPT GPTs・Google Gemini Gems・Google NotebookLM・Anthropic Claude Projects の 4 平台向けに再パッケージしたリリース版 v1.0。現行運用中 (Phase 6.5 完了)。</t>
+          <t>(4) Phase 7 RAG+KG — 検索拡張生成 (RAG) および知識グラフ (KG) を組み合わせた二段階インテリジェント検索・確認システムの設計仕様。現状は設計確定・実装未着手。</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>(4) Phase 7 RAG+KG — 検索拡張生成 (RAG) および知識グラフ (KG) を組み合わせた二段階インテリジェント検索・確認システムの設計仕様。現状は設計確定・実装未着手。</t>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>1.3 想定読者</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="C11" s="18" t="inlineStr">
         <is>
-          <t>出典: METHODOLOGY.md §2 + docs/DESIGN_RAG_KG.md §1.4 + ai_platforms/release/v1.0/。</t>
+          <t>本書の想定読者は、IT 分野および医療データ分野の双方に知見を有する実務担当者である。具体的には、臨床試験データ管理、SDTM データプログラミング、マッピング品質確認、SDTM 教育に従事する技術者および管理者を想定する。01 要件定義書 §1.3 と同一の読者層を対象とする。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>1.3 想定読者</t>
+          <t>1.4 関連文書</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="C13" s="18" t="inlineStr">
         <is>
-          <t>本書の想定読者は、IT 分野および医療データ分野の双方に知見を有する実務担当者である。具体的には、臨床試験データ管理、SDTM データプログラミング、マッピング品質確認、SDTM 教育に従事する技術者および管理者を想定する。01 要件定義書 §1.3 と同一の読者層を対象とする。</t>
+          <t>本書は以下の文書群と連携する。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>出典: docs/jp/01_要件定義書.xlsx §1.3 + docs/jp/PLAN.md §0 受信者欄。</t>
+          <t>・01 要件定義書 (ITMS-SDTM-01): 本書の上位根拠章。機能要件 FR-01〜FR-11、非機能要件 NFR-01〜NFR-06、制約条件 C-01〜C-05 を規定する。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>1.4 関連文書</t>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>・03 運用保守マニュアル (ITMS-SDTM-03): 本書が規定するシステム構成に基づく日常運用手順・保守手順・障害対応を記述する。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>本書は以下の文書群と連携する。</t>
+          <t>・04 テスト結果報告書 (ITMS-SDTM-04): 本書が規定する設計の試験範囲・実施結果・合格判定・根拠資料を記録する。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="C17" s="18" t="inlineStr">
         <is>
-          <t>・01 要件定義書 (ITMS-SDTM-01): 本書の上位根拠章。機能要件 FR-01〜FR-11、非機能要件 NFR-01〜NFR-06、制約条件 C-01〜C-05 を規定する。</t>
+          <t>・05 詳細設計書 (ITMS-SDTM-05): 本書の各章 (特に §3 データモデル) の章別詳細展開を記述する。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>・03 運用保守マニュアル (ITMS-SDTM-03): 本書が規定するシステム構成に基づく日常運用手順・保守手順・障害対応を記述する。</t>
+          <t>・06 トレーサビリティ管理表 (ITMS-SDTM-06): 本書の設計項目と要件・試験・根拠資料の横断対応を記録する。なお「トレーサビリティ管理表」は文書の正式名称 (固有名) であり、概念用語としての「追跡可能性 (traceability)」とは区別して用いる。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>・04 テスト結果報告書 (ITMS-SDTM-04): 本書が規定する設計の試験範囲・実施結果・合格判定・根拠資料を記録する。</t>
+          <t>・99 用語集: 本書で用いる技術用語の英語・日本語・中国語・出典規格の四列対照辞書。</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>・05 詳細設計書 (ITMS-SDTM-05): 本書の各章 (特に §3 データモデル) の章別詳細展開を記述する。</t>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>1.5 設計方針 (中核理念)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>・06 トレーサビリティ管理表 (ITMS-SDTM-06): 本書の設計項目と要件・試験・根拠資料の横断対応を記録する。なお「トレーサビリティ管理表」は文書の正式名称 (固有名) であり、概念用語としての「追跡可能性 (traceability)」とは区別して用いる。</t>
+          <t>本書全体を貫く設計方針は以下の 4 点である。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>・99 用語集: 本書で用いる技術用語の英語・日本語・中国語・出典規格の四列対照辞書。</t>
+          <t>(1) 字面追跡可能性 — 知識ベースの任意の記述について、出典 PDF の対応頁および節を数秒で照合できる構造を設計原則とする。ドメイン・章節・受控用語の各層で追跡経路を完備する。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="C23" s="18" t="inlineStr">
         <is>
-          <t>出典: docs/jp/PLAN.md §1。</t>
+          <t>(2) リスク主導確認 — GAMP 5 (国際製薬技術協会 ISPE 発行) のリスク主導確認の考え方に整合し、宣言された仕様・実行された確認・独立した審査・文書化された不整合追跡を備える。</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>1.5 設計方針 (中核理念)</t>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>(3) ローカル先行・プロバイダー非依存 — Phase 7 RAG+KG はすべて Docker Compose によるローカル実行を前提とし、特定の LLM 供給者に固定しない設計とする。クラウド展開は本設計範囲外とする。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="C25" s="18" t="inlineStr">
         <is>
-          <t>本書全体を貫く設計方針は以下の 4 点である。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>(1) 字面追跡可能性 — 知識ベースの任意の記述について、出典 PDF の対応頁および節を数秒で照合できる構造を設計原則とする。ドメイン・章節・受控用語の各層で追跡経路を完備する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>(2) リスク主導確認 — GAMP 5 (国際製薬技術協会 ISPE 発行) のリスク主導確認の考え方に整合し、宣言された仕様・実行された確認・独立した審査・文書化された不整合追跡を備える。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>(3) ローカル先行・プロバイダー非依存 — Phase 7 RAG+KG はすべて Docker Compose によるローカル実行を前提とし、特定の LLM 供給者に固定しない設計とする。クラウド展開は本設計範囲外とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>(4) 読取専用源 + 派生著作物 — knowledge_base/ ディレクトリは変更不可の読取専用源として扱う。本納品物を含む改修は派生著作物側にのみ適用する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>出典: (1) 字面追跡可能性 = METHODOLOGY.md §3、(2) リスク主導確認 = METHODOLOGY.md §5 + Compliance framing、(3) ローカル先行・プロバイダー非依存 = docs/DESIGN_RAG_KG.md §1.4、(4) 読取専用源 + 派生著作物 = docs/DESIGN_RAG_KG.md §1.4。</t>
+          <t>(4) 読取専用源 + 派生著作物 — knowledge_base/ ディレクトリは変更不可の読取専用源として扱う。関連文書を含む改修は派生著作物側にのみ適用する。</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1430,282 +1395,240 @@
       </c>
     </row>
     <row r="9">
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>出典: METHODOLOGY.md §2 + docs/DESIGN_RAG_KG.md §2 + ai_platforms/release/v1.0/。</t>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>2.2 知識ベース本体</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>2.2 知識ベース本体</t>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>知識ベース本体 (knowledge_base/) は、CDISC 公式刊行物 4 種から 7 工程パイプラインで抽出・再構成した 293 件の Markdown ファイル群である。以下の 5 層で構成される。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="C11" s="18" t="inlineStr">
         <is>
-          <t>知識ベース本体 (knowledge_base/) は、CDISC 公式刊行物 4 種から 7 工程パイプラインで抽出・再構成した 293 件の Markdown ファイル群である。以下の 5 層で構成される。</t>
+          <t>(1) ドメイン層 (knowledge_base/domains/) — 63 ドメイン × 3 件 = 189 ファイル。各ドメインは spec.md (変数仕様、SDTMIG xlsx 源)・assumptions.md (業務上の前提、PDF 源)・examples.md (実装例、PDF 源) の 3 件パターンで構成される。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>(1) ドメイン層 (knowledge_base/domains/) — 63 ドメイン × 3 件 = 189 ファイル。各ドメインは spec.md (変数仕様、SDTMIG xlsx 源)・assumptions.md (業務上の前提、PDF 源)・examples.md (実装例、PDF 源) の 3 件パターンで構成される。</t>
+          <t>(2) 章節層 (knowledge_base/chapters/) — SDTMIG v3.4 の共通章 6 件 (ch01_introduction.md / ch02_fundamentals.md / ch03_submitting_data.md / ch04_general_assumptions.md / ch08_relationships.md / ch10_appendices.md)。ch05〜ch07 および ch09 はドメイン各論章であり SDTMIG v3.4 の章番号体系に準拠した不連続選択である。各ファイルの先頭に PDF 頁範囲を付与し、SDTMIG 目次と直接対応する。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="C13" s="18" t="inlineStr">
         <is>
-          <t>(2) 章節層 (knowledge_base/chapters/) — SDTMIG v3.4 の共通章 6 件 (ch01_introduction.md / ch02_fundamentals.md / ch03_submitting_data.md / ch04_general_assumptions.md / ch08_relationships.md / ch10_appendices.md)。ch05〜ch07 および ch09 はドメイン各論章であり SDTMIG v3.4 の章番号体系に準拠した不連続選択である。各ファイルの先頭に PDF 頁範囲を付与し、SDTMIG 目次と直接対応する。</t>
+          <t>(3) モデル層 (knowledge_base/model/) — SDTM Model v2.0 の概念モデル 6 件 (concepts_and_terms.md 他)。観察クラス・変数役割・特殊目的ドメイン・関連データセットの設計概念を収録する。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>(3) モデル層 (knowledge_base/model/) — SDTM Model v2.0 の概念モデル 6 件 (concepts_and_terms.md 他)。観察クラス・変数役割・特殊目的ドメイン・関連データセットの設計概念を収録する。</t>
+          <t>(4) 受控用語層 (knowledge_base/terminology/) — CDISC 受控用語 (Controlled Terminology) xlsx 2024 年版から生成。1,005 のコードリスト・37,939 用語を三層 (core/ / questionnaires/ / supplementary/) に分類する。各コードリスト文書に CDISC 割当の C 符号 (例: C66731) を保持し、米国国立がん研究所 EVS Browser (NCI EVS Browser) との相互参照を可能とする。terminology/ 配下のファイル数は 91 件である。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="C15" s="18" t="inlineStr">
         <is>
-          <t>(4) 受控用語層 (knowledge_base/terminology/) — CDISC 受控用語 (Controlled Terminology) xlsx 2024 年版から生成。1,005 のコードリスト・37,939 用語を三層 (core/ / questionnaires/ / supplementary/) に分類する。各コードリスト文書に CDISC 割当の C 符号 (例: C66731) を保持し、米国国立がん研究所 EVS Browser (NCI EVS Browser) との相互参照を可能とする。terminology/ 配下のファイル数は 91 件である。</t>
+          <t>(5) 索引層 — INDEX.md (全 293 ファイルのクイックリファレンス、主索引として 1 件扱い) + ROUTING.md (問題種別別参照経路の経路層文書) + VARIABLE_INDEX.md (1,523 変数の逆引き索引)。なお、公式合計 293 件の内訳は「INDEX.md では索引を 1 件として計上」する方式であり、3 ファイルの物理的存在とは区別する。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>(5) 索引層 — INDEX.md (全 293 ファイルのクイックリファレンス、主索引として 1 件扱い) + ROUTING.md (問題種別別参照経路の経路層文書) + VARIABLE_INDEX.md (1,523 変数の逆引き索引)。なお、公式合計 293 件の内訳は「INDEX.md では索引を 1 件として計上」する方式であり、3 ファイルの物理的存在とは区別する。</t>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>5 層の合計: 189 (ドメイン層) + 91 (受控用語層) + 6 (モデル層) + 6 (章節層) + 1 (主索引) = 293 件 (knowledge_base/INDEX.md l.4 の公式合計と一致)。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>5 層の合計: 189 (ドメイン層) + 91 (受控用語層) + 6 (モデル層) + 6 (章節層) + 1 (主索引) = 293 件 (knowledge_base/INDEX.md l.4 の公式合計と一致)。</t>
+          <t>2.3 検証パイプライン</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>出典: knowledge_base/INDEX.md + .work/00_planning/restructure_plan.md §三 + METHODOLOGY.md §3。</t>
+          <t>検証パイプラインは、知識ベース本体の各記述を出典 PDF と頁単位で字面照合する独立工程である。7 工程パイプラインと並行して継続実施されており、本書執筆時点で対象範囲の 97% を完了している。</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>2.3 検証パイプライン</t>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>工程は以下の 3 段階で構成される。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>検証パイプラインは、知識ベース本体の各記述を出典 PDF と頁単位で字面照合する独立工程である。7 工程パイプラインと並行して継続実施されており、本書執筆時点で対象範囲の 97% を完了している。</t>
+          <t>(1) 検証単位抽出 — PDF 原文および知識ベース記述を検証単位として抽出する。各検証単位は一意の識別子で管理し、凍結済データ設計仕様 (v1.2、凍結日: 2026-04-24) に従い構造化データとして記録する。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>工程は以下の 3 段階で構成される。</t>
+          <t>(2) 突合判定 — 各検証単位について突合管理表に記録する。PDF から知識ベースへの順方向および知識ベースから PDF への逆方向の双方で照合結果を判定し、類似度スコア (0.0〜1.0) を数値で記録する。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>(1) 検証単位抽出 — PDF 原子および MD 原子を検証単位データ schema (atom_schema v1.2 凍結済) に従い抽出する。PDF 原子は atom_id 形式 &lt;source_short&gt;_p&lt;NNN&gt;_a&lt;NNN&gt; (例: ig34_p0425_a012) で識別する。MD 原子は md_&lt;file_stem&gt;_a&lt;NNN&gt; (例: md_ch08_a042) で識別する。atom_type は HEADING / SENTENCE / LIST_ITEM / TABLE_HEADER / TABLE_ROW / CODE_LITERAL / CROSS_REF / FIGURE / NOTE の 9 値硬列挙型である。</t>
+          <t>(3) 独立二次審査 — 審査独立性原則に従い、照合を実施した担当者とは異なる主体が審査記録に結果 (確認・修正・保留) を追記する。</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>(2) 突合判定 — 突合管理表データ schema (ledger_schema v1.2 凍結済) に従い、各検証単位について突合管理表の 1 行 JSONL として記録する。順方向 (PDF→MD) の verdict は 9 値 (EXACT / EQUIVALENT / EDITORIAL_CORRECTION / TABLE_SIMPLIFIED / PARTIAL / MISPLACED / ERROR / MISSING / INTENTIONAL_EXCLUDE)、逆方向 (MD→PDF) の verdict は 5 値 (SOURCED / EDITORIAL_ADDITION / SYNTHESIZED / UNSOURCED / HALLUCINATED) である。類似度スコア (similarity_score) は 0.0〜1.0 の範囲で、PARTIAL は 0.50 以上、SOURCED は 0.50 以上が必須条件である。</t>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>2.4 AI 平台展開 (Phase 6.5 完了)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>(3) 独立二次審査 — 審査独立性原則に従い、整合確認担当者とは異なる主体が審査記録 (audited_by 配列) に CONFIRM / OVERRIDE / AMBIGUOUS を追記する。</t>
+          <t>AI 平台展開は、知識ベース本体を 4 種の AI 平台向け配布物として整形したものである。Phase 6.5 として完了し、リリース版 v1.0 として運用中である。</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>出典: .work/06_deep_verification/schema/atom_schema.json + .work/06_deep_verification/schema/ledger_schema.json + METHODOLOGY.md §2 末尾段落。</t>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>4 平台の概要は以下のとおりである。</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>2.4 AI 平台展開 (Phase 6.5 完了)</t>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>・ChatGPT GPTs (v2.2 LIVE) — 20 ファイル上限に整合した結合ファイル構成。ドメイン仕様・受控用語・章節を統合した参照ツール。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="C27" s="18" t="inlineStr">
         <is>
-          <t>AI 平台展開は、知識ベース本体を 4 種の AI 平台向け配布物として整形したものである。Phase 6.5 として完了し、リリース版 v1.0 として運用中である。</t>
+          <t>・Google Gemini Gems (v7.1 LIVE) — 大きなコンテキストウィンドウを活用した 4 ファイル積極結合構成。幻覚防止プロンプトを v7.1 で強化済。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>4 平台の概要は以下のとおりである。</t>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>・Google NotebookLM — 42 ソース構成 (上限 50 のうち 42 使用)。知識ベース内のソースのみに限定した高精度参照モデル。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>・ChatGPT GPTs (v2.2 LIVE) — 20 ファイル上限に整合した結合ファイル構成。ドメイン仕様・受控用語・章節を統合した参照ツール。</t>
+          <t>・Anthropic Claude Projects (v2.6) — 19 ファイル構成 (容量約 77%、約 1.29M トークン使用)。QS コードリスト展開率 約 55.8% (KNOWN_LIMITATIONS.en.md L1 計測)。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>・Google Gemini Gems (v7.1 LIVE) — 大きなコンテキストウィンドウを活用した 4 ファイル積極結合構成。幻覚防止プロンプトを v7.1 で強化済。</t>
+          <t>各平台は容量制約・機能制約に整合させた配布物として再パッケージされており、既知の限界は ai_platforms/release/v1.0/KNOWN_LIMITATIONS.en.md に一覧化されている。</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>・Google NotebookLM — 42 ソース構成 (上限 50 のうち 42 使用)。知識ベース内のソースのみに限定した高精度参照モデル。</t>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>2.5 Phase 7 RAG+KG (設計済・実装未着手)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>・Anthropic Claude Projects (v2.6) — 19 ファイル構成 (容量約 77%、約 1.29M トークン使用)。QS コードリスト展開率 約 55.8% (KNOWN_LIMITATIONS.en.md L1 計測)。</t>
+          <t>Phase 7 RAG+KG は、知識ベースを入力源とした二段階インテリジェント検索・確認システムの設計仕様である。設計は確定しているが、実装は未着手である。本書での扱いは設計書面のみであり、実装到達は別工程による。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>各平台は容量制約・機能制約に整合させた配布物として再パッケージされており、既知の限界は ai_platforms/release/v1.0/KNOWN_LIMITATIONS.en.md に一覧化されている。</t>
+          <t>二段階ロードマップは以下のとおりである。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>出典: ai_platforms/release/v1.0/ + METHODOLOGY.md §2 Phase 6.5。</t>
+          <t>Phase 7 第 1 段階 (RAG + データセット確認): 検索拡張生成 (RAG) パイプラインとして、Markdown ファイルをチャンク化して Chroma ベクトル DB に格納し、LiteLLM 抽象層経由で Claude / GPT 他の LLM を呼び出す。Streamlit インタフェースで意味的質問応答とデータセット確認レポートを提供する設計。前提: 既存の 293 件 Markdown ファイルを利用可能。</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>2.5 Phase 7 RAG+KG (設計済・実装未着手)</t>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>Phase 7 第 2 段階 (KG + 混合経路): 知識グラフ (KG) として Neo4j にノード・リレーションを投入し、Cypher クエリにより横断参照・影響範囲分析を可能にする。意図分類器によりベクトル検索経路・グラフ検索経路・混合経路を自動選択する設計。前提: P3 構造化メタデータ (knowledge_base/domains/&lt;DOMAIN&gt;/meta.yaml) の自動生成スクリプト (docs/DESIGN_RAG_KG.md §5.1 設計済) による出力が完了していること。本書執筆時点で当該生成スクリプトの実装および meta.yaml 出力は未実施。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>Phase 7 RAG+KG は、知識ベースを入力源とした二段階インテリジェント検索・確認システムの設計仕様である。設計は確定しているが、実装は未着手である。本書での扱いは設計書面のみであり、実装到達は別工程による。</t>
+          <t>全コンポーネントは Docker Compose によるローカル実行を前提とし、クラウド展開は本設計範囲外である。</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="C37" s="18" t="inlineStr">
-        <is>
-          <t>二段階ロードマップは以下のとおりである。</t>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>2.6 サブシステム間の関係</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>Phase 7 第 1 段階 (RAG + データセット確認): 検索拡張生成 (RAG) パイプラインとして、Markdown ファイルをチャンク化して Chroma ベクトル DB に格納し、LiteLLM 抽象層経由で Claude / GPT 他の LLM を呼び出す。Streamlit インタフェースで意味的質問応答とデータセット確認レポートを提供する設計。前提: 既存の 293 件 Markdown ファイルを利用可能。</t>
+          <t>各サブシステムの入力・出力関係は以下のとおりである。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>Phase 7 第 2 段階 (KG + 混合経路): 知識グラフ (KG) として Neo4j にノード・リレーションを投入し、Cypher クエリにより横断参照・影響範囲分析を可能にする。意図分類器によりベクトル検索経路・グラフ検索経路・混合経路を自動選択する設計。前提: P3 構造化メタデータ (knowledge_base/domains/&lt;DOMAIN&gt;/meta.yaml) の自動生成スクリプト (docs/DESIGN_RAG_KG.md §5.1 設計済) による出力が完了していること。本書執筆時点で当該生成スクリプトの実装および meta.yaml 出力は未実施。</t>
+          <t>知識ベース本体は、すべてのサブシステムの共通読取専用源である。変更不可の入力として扱い、派生著作物側のみで改修を行う。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>全コンポーネントは Docker Compose によるローカル実行を前提とし、クラウド展開は本設計範囲外である。</t>
+          <t>検証パイプラインは、knowledge_base/ を入力とし、突合管理表 (JSONL 形式) および根拠資料を内部検証管理リポジトリに出力する。知識ベースの品質を支える独立した工程として機能する。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>出典: docs/DESIGN_RAG_KG.md §2 + §7。</t>
+          <t>AI 平台展開は、知識ベースを容量制約・機能制約に整合させた配布物に再パッケージしたものである。知識ベース本体を参照するが、改変はしない。</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="17" t="inlineStr">
-        <is>
-          <t>2.6 サブシステム間の関係</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43" s="18" t="inlineStr">
-        <is>
-          <t>各サブシステムの入力・出力関係は以下のとおりである。</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" s="18" t="inlineStr">
-        <is>
-          <t>知識ベース本体は、すべてのサブシステムの共通読取専用源である。変更不可の入力として扱い、派生著作物側のみで改修を行う。</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" s="18" t="inlineStr">
-        <is>
-          <t>検証パイプラインは、knowledge_base/ を入力とし、突合管理表 (JSONL 形式) および根拠資料を .work/06_deep_verification/ 配下に出力する。知識ベースの品質を支える独立した工程として機能する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="C46" s="18" t="inlineStr">
-        <is>
-          <t>AI 平台展開は、知識ベースを容量制約・機能制約に整合させた配布物に再パッケージしたものである。知識ベース本体を参照するが、改変はしない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="C47" s="18" t="inlineStr">
+      <c r="C42" s="18" t="inlineStr">
         <is>
           <t>Phase 7 RAG+KG は、knowledge_base/ を入力源として意味的検索・グラフ横断クエリ・データセット確認機能を提供する予定である (実装未着手)。ベクトル DB (Chroma) およびグラフ DB (Neo4j) は独立プロジェクトとして別ディレクトリ (sdtm-rag/) で保持する設計。knowledge_base/ を読取専用源とし、本ディレクトリは sdtm-rag/ に派生する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48" s="18" t="inlineStr">
-        <is>
-          <t>出典: METHODOLOGY.md §3 + docs/DESIGN_RAG_KG.md §1.4。</t>
         </is>
       </c>
     </row>
@@ -1849,7 +1772,7 @@
       </c>
       <c r="C6" s="19" t="inlineStr">
         <is>
-          <t>検証単位データ schema (atom_schema v1.2、凍結日: 2026-04-24) に従う。PDF 原子と MD 原子の共存型 (oneOf) で、atom_id 前缀により区別する。PDF 原子の atom_id 形式: &lt;source_short&gt;_p&lt;NNN&gt;_a&lt;NNN&gt; (例: ig34_p0425_a012)。MD 原子の atom_id 形式: md_&lt;file_stem&gt;_a&lt;NNN&gt; (例: md_ch08_a042)。atom_type は 9 値硬列挙型 (HEADING / SENTENCE / LIST_ITEM / TABLE_HEADER / TABLE_ROW / CODE_LITERAL / CROSS_REF / FIGURE / NOTE)。dataset 文件名 (*.xpt 等) は文脈に関わらず CODE_LITERAL として扱う硬規則あり。</t>
+          <t>検証単位データ設計仕様 (v1.2、凍結日: 2026-04-24) に従う。PDF 原文と知識ベース記述の双方を検証単位として扱い、一意の識別子で管理する。検証単位の種別は 9 値の固定分類 (HEADING / SENTENCE / LIST_ITEM / TABLE_HEADER / TABLE_ROW / CODE_LITERAL / CROSS_REF / FIGURE / NOTE) で記録する。</t>
         </is>
       </c>
       <c r="D6" s="19" t="inlineStr">
@@ -1871,7 +1794,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>突合管理表データ schema (ledger_schema v1.2、凍結日: 2026-04-24) に従う。1 行 JSONL = 1 突合決定として記録する。必須フィールド: verdict / similarity_score (0.0〜1.0) / matched_by。順方向 (PDF→MD) verdict は 9 値 (EXACT / EQUIVALENT / EDITORIAL_CORRECTION / TABLE_SIMPLIFIED / PARTIAL / MISPLACED / ERROR / MISSING / INTENTIONAL_EXCLUDE)。逆方向 (MD→PDF) verdict は 5 値 (SOURCED / EDITORIAL_ADDITION / SYNTHESIZED / UNSOURCED / HALLUCINATED)。数値条件: PARTIAL は similarity_score ≥ 0.50、SOURCED は similarity_score ≥ 0.50 が必須。独立二次審査記録は audited_by 配列に追記する。</t>
+          <t>突合管理表データ設計仕様 (v1.2、凍結日: 2026-04-24) に従う。各突合決定を構造化データとして記録する。順方向 (PDF→知識ベース) の照合結果は 9 値、逆方向 (知識ベース→PDF) の照合結果は 5 値の固定分類で判定する。類似度スコアは 0.0〜1.0 の数値で記録し、判定区分ごとに下限値を定める。独立二次審査の結果は審査記録に追記する。</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -1947,7 +1870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2070,28 +1993,6 @@
       <c r="D6" s="19" t="inlineStr">
         <is>
           <t>設計済・未実装</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>IF-05</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>本納品物生成基盤 (内製スクリプト)</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>本納品物 7 文書 (.xlsx) および 99 用語集の生成基盤として、openpyxl 3.1.5 (Python) および内製スクリプト build_xlsx.py / audit_terms.py を使用する。テンプレート (style_guide.xlsx / cover_template.xlsx) で表紙・改訂履歴・目次・承認欄の書式を統一する。YAML 源ファイル (docs/jp/sources/) をスクリプトで変換し .xlsx を生成する方式を採用している。詳細な生成手順は 05 詳細設計書に委譲する。</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>運用中</t>
         </is>
       </c>
     </row>
@@ -2197,7 +2098,7 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>検証単位データ schema (atom_schema) および突合管理表データ schema (ledger_schema) は v1.2 (凍結日: 2026-04-24) に固定されている。P0 Pilot 完了をもって以後の変更を禁ずる旨が schema ファイル自体の frozen_at フィールドおよび frozen_evidence 配列に明記されている。本書 §3.4 および §3.5 の記述はこの凍結版に依拠する。凍結後の schema 変更が必要な場合は本書および 05 詳細設計書の改訂を要する。</t>
+          <t>検証単位データ設計仕様および突合管理表データ設計仕様は v1.2 (凍結日: 2026-04-24) に固定されている。検証パイプライン初期検証完了をもって変更を凍結済とする。本書 §3.4 および §3.5 の記述はこの凍結版に依拠する。凍結後の変更が必要な場合は本書および 05 詳細設計書の改訂を要する。</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2255,7 @@
       </c>
       <c r="C6" s="19" t="inlineStr">
         <is>
-          <t>.work/06_deep_verification/schema/atom_schema.json</t>
+          <t>内部管理リポジトリ（詳細はお問い合わせください）</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2272,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>.work/06_deep_verification/schema/ledger_schema.json</t>
+          <t>内部管理リポジトリ（詳細はお問い合わせください）</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2289,7 @@
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
-          <t>.work/00_planning/restructure_plan.md</t>
+          <t>内部管理リポジトリ（詳細はお問い合わせください）</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2306,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>.work/00_planning/source_relationship.md</t>
+          <t>内部管理リポジトリ（詳細はお問い合わせください）</t>
         </is>
       </c>
     </row>
